--- a/data/trans_orig/IQ39A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana</t>
+          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,56; 40,77</t>
+          <t>35,59; 40,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,68; 42,37</t>
+          <t>33,69; 42,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,75; 44,19</t>
+          <t>37,08; 44,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,35; 40,63</t>
+          <t>37,4; 40,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,84; 41,38</t>
+          <t>35,94; 41,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,53; 44,02</t>
+          <t>34,49; 43,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,16; 42,41</t>
+          <t>36,96; 42,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,19; 39,19</t>
+          <t>35,84; 39,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,56; 40,4</t>
+          <t>36,36; 40,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,5; 42,19</t>
+          <t>35,45; 42,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,36; 42,48</t>
+          <t>38,03; 42,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,19; 39,51</t>
+          <t>37,14; 39,42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,97; 36,78</t>
+          <t>30,93; 37,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,28; 39,33</t>
+          <t>35,19; 39,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,05; 39,22</t>
+          <t>33,93; 39,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,7; 39,44</t>
+          <t>34,97; 39,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,57; 38,13</t>
+          <t>34,19; 37,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,03; 38,7</t>
+          <t>34,49; 38,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,23; 38,55</t>
+          <t>33,27; 38,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,91; 39,66</t>
+          <t>36,0; 39,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 36,99</t>
+          <t>33,71; 36,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,55; 38,57</t>
+          <t>35,59; 38,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 38,25</t>
+          <t>34,86; 38,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,03</t>
+          <t>36,2; 39,14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,04; 43,47</t>
+          <t>39,11; 43,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,35; 37,59</t>
+          <t>32,46; 37,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 37,45</t>
+          <t>32,12; 37,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,68; 38,28</t>
+          <t>33,61; 38,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,07; 43,09</t>
+          <t>39,14; 43,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,4; 41,31</t>
+          <t>36,4; 41,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,08; 37,94</t>
+          <t>33,29; 38,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,56; 43,43</t>
+          <t>36,49; 42,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,51; 42,53</t>
+          <t>39,62; 42,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,42; 39,1</t>
+          <t>35,31; 39,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,87; 37,15</t>
+          <t>33,57; 37,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,83; 39,84</t>
+          <t>35,97; 39,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,95; 42,81</t>
+          <t>38,29; 42,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,28; 42,69</t>
+          <t>36,08; 42,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,62; 37,8</t>
+          <t>28,67; 37,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,71; 41,36</t>
+          <t>35,8; 40,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,92; 41,61</t>
+          <t>38,04; 41,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 40,25</t>
+          <t>34,22; 40,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,22; 38,8</t>
+          <t>29,72; 38,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,89</t>
+          <t>33,63; 41,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,77; 41,52</t>
+          <t>38,8; 41,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,18; 40,77</t>
+          <t>35,77; 40,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,32; 36,5</t>
+          <t>30,61; 36,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,47; 40,26</t>
+          <t>35,33; 39,81</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,78; 40,71</t>
+          <t>33,33; 40,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,04; 39,52</t>
+          <t>29,72; 39,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,6; 41,14</t>
+          <t>32,07; 41,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,37; 40,27</t>
+          <t>38,24; 40,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,66; 38,78</t>
+          <t>31,75; 38,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,47; 42,99</t>
+          <t>35,28; 43,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,44; 49,39</t>
+          <t>38,4; 49,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,6; 41,95</t>
+          <t>37,78; 41,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,44; 38,81</t>
+          <t>33,63; 38,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,23; 40,46</t>
+          <t>34,29; 40,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,71; 43,91</t>
+          <t>37,68; 44,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,49; 40,87</t>
+          <t>38,44; 40,89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1416,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,47; 43,79</t>
+          <t>39,47; 43,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,93; 39,98</t>
+          <t>32,8; 39,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,21; 46,27</t>
+          <t>40,63; 46,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,34; 38,34</t>
+          <t>32,48; 38,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,0; 44,86</t>
+          <t>40,21; 45,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,47; 43,83</t>
+          <t>34,55; 43,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,43; 46,68</t>
+          <t>40,69; 46,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,88; 40,43</t>
+          <t>37,96; 40,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,63; 43,74</t>
+          <t>40,43; 43,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,86; 41,24</t>
+          <t>34,95; 41,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41,37; 45,77</t>
+          <t>41,44; 45,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,26; 39,21</t>
+          <t>36,29; 39,18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,4; 43,01</t>
+          <t>39,49; 42,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,44; 39,64</t>
+          <t>35,66; 39,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,58; 37,57</t>
+          <t>33,64; 37,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,34; 37,78</t>
+          <t>34,13; 37,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,18; 39,7</t>
+          <t>35,11; 39,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,52; 39,7</t>
+          <t>35,43; 39,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,16; 37,46</t>
+          <t>34,02; 37,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,77; 37,46</t>
+          <t>33,73; 37,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,07; 40,9</t>
+          <t>38,03; 40,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,26; 39,1</t>
+          <t>36,29; 39,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,44; 37,01</t>
+          <t>34,35; 36,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,48; 37,11</t>
+          <t>34,51; 37,11</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,57; 41,02</t>
+          <t>37,72; 41,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,1; 38,62</t>
+          <t>36,02; 38,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,08; 38,87</t>
+          <t>36,01; 38,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,81; 39,9</t>
+          <t>35,76; 39,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,05; 40,86</t>
+          <t>37,82; 40,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,81; 39,04</t>
+          <t>35,79; 39,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,14; 39,55</t>
+          <t>36,06; 39,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,52; 40,76</t>
+          <t>36,54; 40,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,38; 40,56</t>
+          <t>38,24; 40,51</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36,29; 38,41</t>
+          <t>36,4; 38,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,61; 38,82</t>
+          <t>36,57; 38,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,75; 39,57</t>
+          <t>36,7; 39,66</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,55; 40,25</t>
+          <t>38,57; 40,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,54; 38,37</t>
+          <t>36,62; 38,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,0; 37,93</t>
+          <t>36,14; 38,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36,58; 38,16</t>
+          <t>36,55; 38,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,13; 39,72</t>
+          <t>38,24; 39,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,86; 38,83</t>
+          <t>36,9; 38,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,76; 38,72</t>
+          <t>36,64; 38,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,5</t>
+          <t>36,97; 38,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,76</t>
+          <t>38,62; 39,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37,05; 38,35</t>
+          <t>37,02; 38,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36,73; 38,01</t>
+          <t>36,69; 37,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,17</t>
+          <t>37,01; 38,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,59; 40,52</t>
+          <t>35,52; 40,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,69; 42,4</t>
+          <t>33,93; 42,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,08; 44,69</t>
+          <t>37,17; 44,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,4; 40,62</t>
+          <t>37,33; 40,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,94; 41,2</t>
+          <t>35,5; 40,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,49; 43,79</t>
+          <t>34,88; 44,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 42,79</t>
+          <t>37,27; 42,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,84; 39,19</t>
+          <t>36,12; 39,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,36; 40,23</t>
+          <t>36,71; 40,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,45; 42,19</t>
+          <t>35,36; 41,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,03; 42,32</t>
+          <t>38,06; 42,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,14; 39,42</t>
+          <t>37,2; 39,44</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,93; 37,07</t>
+          <t>30,71; 36,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 39,42</t>
+          <t>35,0; 39,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,93; 39,15</t>
+          <t>34,07; 39,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,97; 39,66</t>
+          <t>34,67; 39,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,19; 37,83</t>
+          <t>34,4; 38,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,49; 38,89</t>
+          <t>34,21; 38,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,27; 38,65</t>
+          <t>33,55; 38,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,0; 39,78</t>
+          <t>35,89; 39,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,71; 36,92</t>
+          <t>33,57; 37,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,59; 38,63</t>
+          <t>35,53; 38,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 38,38</t>
+          <t>34,58; 38,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,2; 39,14</t>
+          <t>36,14; 39,03</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,11; 43,3</t>
+          <t>38,92; 43,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,46; 37,59</t>
+          <t>32,15; 37,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,12; 37,34</t>
+          <t>32,12; 37,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,61; 38,36</t>
+          <t>33,59; 38,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,14; 43,5</t>
+          <t>39,24; 43,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,4; 41,37</t>
+          <t>35,98; 41,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,29; 38,03</t>
+          <t>33,11; 37,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,49; 42,55</t>
+          <t>36,73; 42,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,62; 42,6</t>
+          <t>39,55; 42,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 39,17</t>
+          <t>35,45; 39,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,57; 37,17</t>
+          <t>33,82; 37,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,97; 39,57</t>
+          <t>35,79; 39,89</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,29; 42,83</t>
+          <t>38,13; 43,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 42,7</t>
+          <t>36,07; 42,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 37,48</t>
+          <t>28,67; 37,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,8; 40,83</t>
+          <t>35,76; 40,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,04; 41,59</t>
+          <t>38,17; 41,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 40,32</t>
+          <t>34,2; 40,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,72; 38,21</t>
+          <t>29,64; 38,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,63; 41,31</t>
+          <t>33,51; 40,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,8; 41,65</t>
+          <t>38,67; 41,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,77; 40,59</t>
+          <t>36,08; 40,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,61; 36,95</t>
+          <t>30,63; 36,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,33; 39,81</t>
+          <t>35,52; 40,24</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,33; 40,43</t>
+          <t>33,28; 40,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 39,61</t>
+          <t>30,52; 40,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,07; 41,22</t>
+          <t>31,69; 41,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,26</t>
+          <t>38,29; 40,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,75; 38,95</t>
+          <t>31,92; 39,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,28; 43,0</t>
+          <t>35,43; 42,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,4; 49,78</t>
+          <t>38,5; 48,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,78; 41,97</t>
+          <t>37,66; 41,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,63; 38,86</t>
+          <t>33,79; 39,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,29; 40,58</t>
+          <t>34,24; 40,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,68; 44,26</t>
+          <t>37,13; 44,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,44; 40,89</t>
+          <t>38,35; 40,79</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,47; 43,55</t>
+          <t>39,56; 44,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,8; 39,75</t>
+          <t>32,72; 40,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,63; 46,65</t>
+          <t>40,16; 46,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,48; 38,27</t>
+          <t>32,38; 38,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,21; 45,18</t>
+          <t>40,27; 45,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,55; 43,39</t>
+          <t>34,58; 44,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,69; 46,68</t>
+          <t>40,68; 46,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,96; 40,49</t>
+          <t>37,96; 40,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,43; 43,84</t>
+          <t>40,51; 43,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,95; 41,02</t>
+          <t>34,98; 40,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41,44; 45,79</t>
+          <t>41,49; 45,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,29; 39,18</t>
+          <t>36,48; 39,28</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,49; 42,88</t>
+          <t>39,47; 43,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,66; 39,82</t>
+          <t>35,54; 39,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,64; 37,59</t>
+          <t>33,3; 37,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,13; 37,76</t>
+          <t>34,23; 37,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,11; 39,69</t>
+          <t>34,94; 39,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,43; 39,51</t>
+          <t>35,7; 39,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,02; 37,68</t>
+          <t>33,88; 37,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,73; 37,47</t>
+          <t>33,66; 37,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,03; 40,84</t>
+          <t>38,0; 40,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,29; 39,2</t>
+          <t>36,17; 39,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,35; 36,94</t>
+          <t>34,33; 36,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,51; 37,11</t>
+          <t>34,63; 37,08</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,72; 41,15</t>
+          <t>37,7; 41,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,02; 38,67</t>
+          <t>36,12; 38,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,01; 38,92</t>
+          <t>36,21; 38,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,76; 39,79</t>
+          <t>35,74; 40,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,82; 40,86</t>
+          <t>37,93; 40,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,79; 39,05</t>
+          <t>35,84; 39,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,06; 39,59</t>
+          <t>36,18; 39,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,54; 40,72</t>
+          <t>36,41; 40,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,51</t>
+          <t>38,27; 40,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36,4; 38,65</t>
+          <t>36,42; 38,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,57; 38,79</t>
+          <t>36,71; 38,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,7; 39,66</t>
+          <t>36,7; 39,68</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,57; 40,24</t>
+          <t>38,67; 40,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,62; 38,38</t>
+          <t>36,64; 38,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,14; 38,08</t>
+          <t>35,99; 37,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36,55; 38,17</t>
+          <t>36,59; 38,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,24; 39,72</t>
+          <t>38,17; 39,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,9; 38,84</t>
+          <t>36,94; 38,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,48</t>
+          <t>36,64; 38,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,97; 38,59</t>
+          <t>36,83; 38,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,62; 39,71</t>
+          <t>38,64; 39,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37,02; 38,35</t>
+          <t>37,05; 38,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36,69; 37,96</t>
+          <t>36,66; 37,99</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,08</t>
+          <t>37,0; 38,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,89</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37,98</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>38,34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>38,21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>40,71</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,82</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,18</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,89</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,96</t>
+          <t>38,68</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,38</t>
+          <t>38,31</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,52; 40,51</t>
+          <t>35,84; 41,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,93; 42,77</t>
+          <t>34,53; 44,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,17; 44,16</t>
+          <t>37,16; 42,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,33; 40,75</t>
+          <t>36,44; 39,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,5; 40,99</t>
+          <t>35,56; 40,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,88; 44,52</t>
+          <t>33,68; 42,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 42,4</t>
+          <t>36,75; 44,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,12; 39,27</t>
+          <t>37,29; 40,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,71; 40,47</t>
+          <t>36,56; 40,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,36; 41,98</t>
+          <t>35,5; 42,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,06; 42,39</t>
+          <t>38,36; 42,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,2; 39,44</t>
+          <t>37,35; 39,38</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,88</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36,34</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37,97</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>34,17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>37,49</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>37,0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,3</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,44</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,88</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>36,34</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,03</t>
+          <t>37,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,7</t>
+          <t>37,63</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,71; 36,69</t>
+          <t>34,57; 38,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,0; 39,33</t>
+          <t>34,03; 38,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,07; 39,09</t>
+          <t>33,23; 38,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 39,18</t>
+          <t>35,71; 39,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,4; 38,0</t>
+          <t>30,97; 36,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,21; 38,59</t>
+          <t>35,28; 39,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,55; 38,61</t>
+          <t>34,05; 39,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,89; 39,86</t>
+          <t>34,66; 39,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 37,04</t>
+          <t>33,58; 36,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,53; 38,76</t>
+          <t>35,55; 38,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,58; 38,42</t>
+          <t>34,62; 38,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,14; 39,03</t>
+          <t>36,08; 39,02</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38,79</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>41,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>35,41</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>35,24</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36,36</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41,11</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,06</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,09</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,82</t>
+          <t>36,54</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,58</t>
+          <t>37,62</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,92; 43,24</t>
+          <t>39,07; 43,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,15; 37,57</t>
+          <t>36,4; 41,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,12; 37,44</t>
+          <t>33,08; 37,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,59; 38,29</t>
+          <t>36,55; 43,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,24; 43,34</t>
+          <t>39,04; 43,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,98; 41,3</t>
+          <t>32,35; 37,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,11; 37,95</t>
+          <t>32,67; 37,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,73; 42,85</t>
+          <t>33,92; 38,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,55; 42,58</t>
+          <t>39,51; 42,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,45; 39,2</t>
+          <t>35,42; 39,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,82; 37,28</t>
+          <t>33,87; 37,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,79; 39,89</t>
+          <t>35,92; 39,7</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39,79</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37,42</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36,9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>40,49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>39,4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>33,09</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,79</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,42</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,2</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,02</t>
+          <t>38,07</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,52</t>
+          <t>37,5</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,13; 43,0</t>
+          <t>37,92; 41,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,07; 42,75</t>
+          <t>34,22; 40,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 37,45</t>
+          <t>30,22; 38,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 40,94</t>
+          <t>33,69; 41,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,17; 41,57</t>
+          <t>37,95; 42,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,2; 40,82</t>
+          <t>36,28; 42,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 38,55</t>
+          <t>28,62; 37,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,51; 40,85</t>
+          <t>35,66; 41,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,67; 41,6</t>
+          <t>38,77; 41,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 40,58</t>
+          <t>36,18; 40,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,63; 36,74</t>
+          <t>30,32; 36,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,52; 40,24</t>
+          <t>35,34; 40,39</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35,75</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,93</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40,04</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>37,41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>35,57</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>37,88</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,75</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,19</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>41,93</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,33</t>
+          <t>39,34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39,83</t>
+          <t>39,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 40,42</t>
+          <t>31,66; 38,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,52; 40,4</t>
+          <t>35,47; 42,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,69; 41,28</t>
+          <t>38,44; 49,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,29; 40,3</t>
+          <t>37,23; 41,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,92; 39,05</t>
+          <t>33,78; 40,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,43; 42,87</t>
+          <t>30,04; 39,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,5; 48,98</t>
+          <t>31,6; 41,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,66; 41,88</t>
+          <t>38,36; 40,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,79; 39,06</t>
+          <t>33,44; 38,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 40,78</t>
+          <t>34,23; 40,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,13; 44,23</t>
+          <t>36,71; 43,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,35; 40,79</t>
+          <t>38,28; 40,61</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42,66</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38,52</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43,63</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39,16</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>41,51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>36,6</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>43,27</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35,88</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42,66</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,52</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,63</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39,17</t>
+          <t>35,58</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,92</t>
+          <t>37,67</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,56; 44,05</t>
+          <t>40,0; 44,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,72; 40,21</t>
+          <t>34,47; 43,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,16; 46,71</t>
+          <t>40,43; 46,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,38; 38,34</t>
+          <t>37,81; 40,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,27; 45,21</t>
+          <t>39,47; 43,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,58; 44,42</t>
+          <t>32,93; 39,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,68; 46,85</t>
+          <t>40,21; 46,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,96; 40,61</t>
+          <t>31,86; 38,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,51; 43,95</t>
+          <t>40,63; 43,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,98; 40,88</t>
+          <t>34,86; 41,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41,49; 45,74</t>
+          <t>41,37; 45,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,48; 39,28</t>
+          <t>35,8; 39,0</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37,62</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35,92</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>41,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37,7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>35,45</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36,18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>37,59</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,62</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,0</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35,76</t>
+          <t>36,47</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,94</t>
+          <t>36,17</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,47; 43,04</t>
+          <t>35,18; 39,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,54; 39,89</t>
+          <t>35,52; 39,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,3; 37,27</t>
+          <t>34,16; 37,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,23; 37,77</t>
+          <t>33,87; 37,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,94; 39,74</t>
+          <t>39,4; 43,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,7; 39,79</t>
+          <t>35,44; 39,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,88; 37,47</t>
+          <t>33,58; 37,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,66; 37,57</t>
+          <t>34,79; 37,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,0; 40,84</t>
+          <t>38,07; 40,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,17; 39,06</t>
+          <t>36,26; 39,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,33; 36,82</t>
+          <t>34,44; 37,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,63; 37,08</t>
+          <t>34,77; 37,35</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>39,44</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>37,58</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37,85</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>38,17</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>39,5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>37,56</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>37,65</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>37,69</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>39,44</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>37,85</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38,23</t>
+          <t>37,74</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,99</t>
+          <t>37,97</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,7; 41,2</t>
+          <t>38,05; 40,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,12; 38,72</t>
+          <t>35,81; 39,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,21; 38,91</t>
+          <t>36,14; 39,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,74; 40,0</t>
+          <t>36,48; 40,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,93; 40,89</t>
+          <t>37,57; 41,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,84; 39,14</t>
+          <t>36,1; 38,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,58</t>
+          <t>36,08; 38,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,41; 40,74</t>
+          <t>35,69; 39,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,27; 40,57</t>
+          <t>38,38; 40,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36,42; 38,61</t>
+          <t>36,29; 38,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,71; 38,86</t>
+          <t>36,61; 38,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,7; 39,68</t>
+          <t>36,76; 39,52</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>38,96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37,9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37,65</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>37,72</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>39,46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>37,51</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>37,03</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>37,38</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>37,42</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,57</t>
+          <t>37,58</t>
         </is>
       </c>
     </row>
@@ -1836,47 +1836,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,67; 40,31</t>
+          <t>38,13; 39,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,43</t>
+          <t>36,86; 38,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,99; 37,95</t>
+          <t>36,76; 38,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36,59; 38,2</t>
+          <t>36,86; 38,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,17; 39,66</t>
+          <t>38,55; 40,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,92</t>
+          <t>36,54; 38,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,54</t>
+          <t>36,0; 37,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,83; 38,5</t>
+          <t>36,67; 38,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,64; 39,72</t>
+          <t>38,59; 39,76</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36,66; 37,99</t>
+          <t>36,73; 38,01</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,0; 38,19</t>
+          <t>37,03; 38,17</t>
         </is>
       </c>
     </row>
